--- a/data/trans_orig/IP74A4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A4_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de las cuotas de seguros en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
